--- a/ExcelToJsonWizard-main/excel_files/Enum.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/Enum.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98E39E4-3C0C-4CFE-8AAE-E93DFA59A86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CF91EA-4FDC-4E91-9BCD-67C435E562BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="2250" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="2355" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ItemCarryType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,6 +40,18 @@
   </si>
   <si>
     <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LanguageType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -368,11 +380,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
@@ -391,6 +403,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelToJsonWizard-main/excel_files/Enum.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CF91EA-4FDC-4E91-9BCD-67C435E562BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADB3AFA-C3CA-49E8-8893-5628FA26FFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="2355" windowWidth="14325" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>ItemCarryType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,22 @@
   </si>
   <si>
     <t>Korean</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LeftMouse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetKeyType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -380,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -389,7 +405,7 @@
     <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -412,6 +428,23 @@
       </c>
       <c r="C2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard-main/excel_files/Enum.xlsx
+++ b/ExcelToJsonWizard-main/excel_files/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjectKeubung\GitHub\Invisiphobia_NullPath\ExcelToJsonWizard-main\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADB3AFA-C3CA-49E8-8893-5628FA26FFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29C65C0-CB97-4E9B-BB9E-63BCA9C1A2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ItemCarryType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,22 +52,6 @@
   </si>
   <si>
     <t>Korean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LeftMouse</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GetKeyType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -405,7 +389,7 @@
     <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -428,23 +412,6 @@
       </c>
       <c r="C2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
